--- a/SAS/Extra/Top 10 SQL Queries.xlsx
+++ b/SAS/Extra/Top 10 SQL Queries.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb718e96a9bce2f6/Desktop/Study/SAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/F/Shashi/Study/SAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{01EC0AE1-34CC-4088-A6EA-13A3615AD6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3ADB7A8-70D3-4722-A1E5-2167F83BF292}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E49585-A364-5340-B04E-CBB9CDE12258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{57C4106E-CD5D-FB40-9F34-DC22DD738717}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="7" xr2:uid="{57C4106E-CD5D-FB40-9F34-DC22DD738717}"/>
   </bookViews>
   <sheets>
     <sheet name="Q1" sheetId="1" r:id="rId1"/>
     <sheet name="Q2" sheetId="2" r:id="rId2"/>
     <sheet name="Q3" sheetId="3" r:id="rId3"/>
     <sheet name="Q4" sheetId="11" r:id="rId4"/>
-    <sheet name="Q5" sheetId="12" r:id="rId5"/>
+    <sheet name="Q4b" sheetId="21" r:id="rId5"/>
     <sheet name="Q12" sheetId="20" r:id="rId6"/>
-    <sheet name="Q11" sheetId="19" r:id="rId7"/>
-    <sheet name="Q6" sheetId="13" r:id="rId8"/>
-    <sheet name="Q7" sheetId="14" r:id="rId9"/>
-    <sheet name="Q8" sheetId="15" r:id="rId10"/>
-    <sheet name="Q9" sheetId="16" r:id="rId11"/>
-    <sheet name="Q10" sheetId="17" r:id="rId12"/>
-    <sheet name="solution" sheetId="18" r:id="rId13"/>
+    <sheet name="Q5" sheetId="12" r:id="rId7"/>
+    <sheet name="Q11" sheetId="19" r:id="rId8"/>
+    <sheet name="Q6" sheetId="13" r:id="rId9"/>
+    <sheet name="Q7" sheetId="14" r:id="rId10"/>
+    <sheet name="Q8" sheetId="15" r:id="rId11"/>
+    <sheet name="Q9" sheetId="16" r:id="rId12"/>
+    <sheet name="Q10" sheetId="17" r:id="rId13"/>
+    <sheet name="solution" sheetId="18" r:id="rId14"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="136">
   <si>
     <t>Delete duplicate data</t>
   </si>
@@ -226,13 +227,241 @@
   </si>
   <si>
     <t>drop I  total_count;</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>son</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>GRAND FATHER</t>
+  </si>
+  <si>
+    <t>GRAND SON</t>
+  </si>
+  <si>
+    <t>Emp id</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>manager id</t>
+  </si>
+  <si>
+    <t>Manager name</t>
+  </si>
+  <si>
+    <t>proc sql;</t>
+  </si>
+  <si>
+    <t>create table one as</t>
+  </si>
+  <si>
+    <t>from two;</t>
+  </si>
+  <si>
+    <t>quit;</t>
+  </si>
+  <si>
+    <t>select *,max(Salary) over(partition by dept) as highest_salary,min(salary) over(partition by dept) as lowest_salary</t>
+  </si>
+  <si>
+    <t>SELECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cars,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  days,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cumulative_distance - LAG(cumulative_distance, 1, 0) OVER (PARTITION BY cars ORDER BY days) AS actual_distance</t>
+  </si>
+  <si>
+    <t>FROM cars_travel;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  LEAST(source, destination) AS city1,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  GREATEST(source, destination) AS city2,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  distance</t>
+  </si>
+  <si>
+    <t>FROM routes</t>
+  </si>
+  <si>
+    <t>GROUP BY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  LEAST(source, destination),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  GREATEST(source, destination),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  distance;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  r1.source,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  r1.destination,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  r1.distance</t>
+  </si>
+  <si>
+    <t>FROM routes r1</t>
+  </si>
+  <si>
+    <t>LEFT JOIN routes r2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ON r1.source = r2.destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AND r1.destination = r2.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AND r1.source &gt; r1.destination</t>
+  </si>
+  <si>
+    <t>WHERE r2.source IS NULL;</t>
+  </si>
+  <si>
+    <t>custid</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>destination</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Kochi</t>
+  </si>
+  <si>
+    <t>Mangalore</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>Varanasi</t>
+  </si>
+  <si>
+    <t>/* Step 1: Get starting points (origin not in destination for same customer) */</t>
+  </si>
+  <si>
+    <t>create table start_points as</t>
+  </si>
+  <si>
+    <t>select distinct a.cust_id, a.origin</t>
+  </si>
+  <si>
+    <t>from Flights as a</t>
+  </si>
+  <si>
+    <t>left join Flights as b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  on a.cust_id = b.cust_id and a.origin = b.destination</t>
+  </si>
+  <si>
+    <t>where b.destination is null;</t>
+  </si>
+  <si>
+    <t>/* Step 2: Get final destinations (destination not in origin for same customer) */</t>
+  </si>
+  <si>
+    <t>create table end_points as</t>
+  </si>
+  <si>
+    <t>select distinct a.cust_id, a.destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  on a.cust_id = b.cust_id and a.destination = b.origin</t>
+  </si>
+  <si>
+    <t>where b.origin is null;</t>
+  </si>
+  <si>
+    <t>/* Step 3: Combine both to get final output */</t>
+  </si>
+  <si>
+    <t>create table final_output as</t>
+  </si>
+  <si>
+    <t>select s.cust_id, s.origin, e.destination as final_destination</t>
+  </si>
+  <si>
+    <t>from start_points as s</t>
+  </si>
+  <si>
+    <t>join end_points as e</t>
+  </si>
+  <si>
+    <t>on s.cust_id = e.cust_id;</t>
+  </si>
+  <si>
+    <t>select customerid ,month(saledate) as month,sum(amount) as total_amount from two group by customerid ,month(saledate);</t>
+  </si>
+  <si>
+    <t>proc transpose data=one out=three;</t>
+  </si>
+  <si>
+    <t>by customerid;</t>
+  </si>
+  <si>
+    <t>var total_amount;</t>
+  </si>
+  <si>
+    <t>id month;</t>
+  </si>
+  <si>
+    <t># Pivot the data: each month becomes a column</t>
+  </si>
+  <si>
+    <t>pivot_df = df.pivot(index='customerid', columns='month', values='total_amount')</t>
+  </si>
+  <si>
+    <t>]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -302,8 +531,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,8 +576,38 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -349,11 +615,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -387,6 +668,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,7 +714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6502EBE3-8B73-5C1B-E609-91E9E731C760}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -468,7 +758,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23603E50-E55C-63EA-DE02-D28B67A96896}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -502,6 +792,55 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>111124</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>55561</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>579438</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>171020</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1889124" y="944561"/>
+          <a:ext cx="9548814" cy="8751459"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>15875</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>198437</xdr:rowOff>
@@ -517,7 +856,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1127CEA-CD5A-C810-E991-D0063E48359F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -561,7 +900,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{105C2B3C-81F4-A948-FBDE-397B877318DA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -590,7 +929,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -610,7 +949,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9818B715-EA15-8A57-B9AA-C7F1266AF42A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -654,7 +993,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFDA7EA4-5B04-A3B8-D661-CEDB44C462D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -683,7 +1022,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -703,7 +1042,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BADC7EF-26C5-7C30-8259-EDDDC2150432}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -747,7 +1086,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A03DB561-DC0B-2E8D-B31B-FA3B688EBDD4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -776,7 +1115,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -789,9 +1128,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>107950</xdr:colOff>
+          <xdr:colOff>127000</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>120650</xdr:rowOff>
+          <xdr:rowOff>139700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -801,7 +1140,7 @@
                   <a14:compatExt spid="_x0000_s11265"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-0000012C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-0000012C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -816,11 +1155,11 @@
               <a:avLst/>
             </a:prstGeom>
             <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+              <a:srgbClr val="FFFFFF"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:miter lim="800000"/>
               <a:headEnd/>
@@ -848,15 +1187,15 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>98426</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>111125</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F7EFD38-71A9-5761-0BC9-75730C233D85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -900,7 +1239,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A4847B2-0429-C10F-3300-69D5417F1A31}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -949,7 +1288,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A67AAAF6-7D98-555B-501D-4C01CE7D219B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -993,7 +1332,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE00ED80-4267-19F0-B4CE-6B1AF9FB2D06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1034,15 +1373,15 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>106362</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>36513</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>131763</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBA863C5-4A1F-5C81-6060-533EC12DCEB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1078,15 +1417,15 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>127001</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>127001</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86C37C20-CCF5-8AD9-58CB-FA688D537A0A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1102,8 +1441,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1778001" y="4810126"/>
-          <a:ext cx="5905500" cy="1778000"/>
+          <a:off x="1778001" y="4688418"/>
+          <a:ext cx="6053667" cy="2582332"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1116,6 +1455,268 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>161860</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>44533</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5607338" cy="1619333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>394060</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>184331</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="393700"/>
+          <a:ext cx="6998060" cy="3530781"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>317501</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>39688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>551112</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>103232</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8223251" y="39688"/>
+          <a:ext cx="4845299" cy="857294"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>174624</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>103188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>420686</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Arrow: Up 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8739187" y="2484438"/>
+          <a:ext cx="246062" cy="230187"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>206375</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>63501</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>452437</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Arrow: Up 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11406188" y="2444751"/>
+          <a:ext cx="246062" cy="230187"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1135,7 +1736,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22613431-C505-BDB2-5E45-E9BB07E633F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1179,7 +1780,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D952B87-2053-AB5B-8BA0-969DDE6647EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1223,7 +1824,7 @@
         <xdr:cNvPr id="5121" name="AutoShape 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED13DBCB-DEA5-7E40-A895-F1121895BE36}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000001140000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1271,7 +1872,7 @@
         <xdr:cNvPr id="5123" name="AutoShape 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE703930-ACAC-0393-B7B6-5568E815D7E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003140000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1319,7 +1920,7 @@
         <xdr:cNvPr id="5125" name="AutoShape 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940D9652-3C44-2FF4-B79D-647E1785BCBD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005140000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1352,100 +1953,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>394060</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>184331</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43C4FE3B-4C52-2670-6364-5D474E152944}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="660400" y="393700"/>
-          <a:ext cx="6998060" cy="3530781"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>381001</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>134937</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>614612</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>44</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF9F5403-2275-8A10-E545-988A5ABFEF2B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8286751" y="1524000"/>
-          <a:ext cx="4845299" cy="857294"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1465,7 +1973,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C10BEE5-FE58-67C0-DB7D-E7C460C86550}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1509,7 +2017,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ED1237B-62D5-7B42-74F6-FA18C177BF3C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1553,7 +2061,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA7373F-FA8E-E7EE-1CCC-F759E4167E47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1582,7 +2090,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1602,7 +2110,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF78317C-73F9-F274-F220-36034DCDADD3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1646,7 +2154,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8E66897-16AE-8266-4BB8-757F47541A11}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1690,7 +2198,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{450BBF49-B590-6A95-E16D-DE440A751A8F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1719,59 +2227,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>111124</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>55561</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>579438</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>139270</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91669A8D-6884-FDDE-F7C8-631685C9BB8F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1889124" y="944561"/>
-          <a:ext cx="9548814" cy="8751459"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1809,7 +2268,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1915,7 +2374,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2057,7 +2516,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2069,17 +2528,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2087,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2095,43 +2554,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:18" ht="21" x14ac:dyDescent="0.25">
       <c r="P17" s="14" t="s">
         <v>57</v>
       </c>
       <c r="Q17" s="14"/>
       <c r="R17" s="14"/>
     </row>
-    <row r="18" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:18" ht="21" x14ac:dyDescent="0.25">
       <c r="P18" s="14" t="s">
         <v>58</v>
       </c>
       <c r="Q18" s="14"/>
       <c r="R18" s="14"/>
     </row>
-    <row r="19" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:18" ht="21" x14ac:dyDescent="0.25">
       <c r="P19" s="14" t="s">
         <v>56</v>
       </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
     </row>
-    <row r="20" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:18" ht="21" x14ac:dyDescent="0.25">
       <c r="P20" s="14"/>
       <c r="Q20" s="14"/>
       <c r="R20" s="14"/>
     </row>
-    <row r="21" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:18" ht="21" x14ac:dyDescent="0.25">
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
       <c r="R21" s="14"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>16</v>
       </c>
@@ -2143,22 +2602,132 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D51689-B37C-0541-BD58-346F20EDF6DA}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:Q37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="5"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q14" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q15" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q16" s="19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="17:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q17" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="17:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q20" s="19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="17:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q21" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="17:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q22" s="19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="17:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q23" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="17:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q24" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="17:17" x14ac:dyDescent="0.2">
+      <c r="Q29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="17:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="Q30" s="19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFAA54E8-9519-6F43-9071-FDA35720B37F}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -2166,7 +2735,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2174,21 +2743,265 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="N4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="N5" s="15">
+        <v>1</v>
+      </c>
+      <c r="O5" s="15"/>
+      <c r="Q5" s="15">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="N6" s="15">
+        <v>2</v>
+      </c>
+      <c r="O6" s="16">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>2</v>
+      </c>
+      <c r="R6" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N7" s="15">
+        <v>3</v>
+      </c>
+      <c r="O7" s="16">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>3</v>
+      </c>
+      <c r="R7" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N8" s="15">
+        <v>4</v>
+      </c>
+      <c r="O8" s="16">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>4</v>
+      </c>
+      <c r="R8" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N9" s="15">
+        <v>5</v>
+      </c>
+      <c r="O9" s="15">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>5</v>
+      </c>
+      <c r="R9" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N10" s="15">
+        <v>6</v>
+      </c>
+      <c r="O10" s="15">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>6</v>
+      </c>
+      <c r="R10" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N11" s="15">
+        <v>7</v>
+      </c>
+      <c r="O11" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>7</v>
+      </c>
+      <c r="R11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N12" s="15">
+        <v>8</v>
+      </c>
+      <c r="O12" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>8</v>
+      </c>
+      <c r="R12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N13" s="15">
+        <v>9</v>
+      </c>
+      <c r="O13" s="15">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>9</v>
+      </c>
+      <c r="R13" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N14" s="15">
+        <v>10</v>
+      </c>
+      <c r="O14" s="15">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>10</v>
+      </c>
+      <c r="R14" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N19" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O19" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="P19" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N20" s="15">
+        <v>1</v>
+      </c>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N21" s="15">
+        <v>2</v>
+      </c>
+      <c r="O21" s="16">
+        <v>5</v>
+      </c>
+      <c r="P21" s="15"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N22" s="15">
+        <v>3</v>
+      </c>
+      <c r="O22" s="16">
+        <v>5</v>
+      </c>
+      <c r="P22" s="15"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N23" s="15">
+        <v>4</v>
+      </c>
+      <c r="O23" s="16">
+        <v>5</v>
+      </c>
+      <c r="P23" s="15"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N24" s="15">
+        <v>5</v>
+      </c>
+      <c r="O24" s="15">
+        <v>7</v>
+      </c>
+      <c r="P24" s="15"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N25" s="15">
+        <v>6</v>
+      </c>
+      <c r="O25" s="15">
+        <v>7</v>
+      </c>
+      <c r="P25" s="15"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>16</v>
       </c>
+      <c r="N26" s="15">
+        <v>7</v>
+      </c>
+      <c r="O26" s="15">
+        <v>1</v>
+      </c>
+      <c r="P26" s="15"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N27" s="15">
+        <v>8</v>
+      </c>
+      <c r="O27" s="15">
+        <v>1</v>
+      </c>
+      <c r="P27" s="15"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N28" s="15">
+        <v>9</v>
+      </c>
+      <c r="O28" s="15">
+        <v>8</v>
+      </c>
+      <c r="P28" s="15"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N29" s="15">
+        <v>10</v>
+      </c>
+      <c r="O29" s="15">
+        <v>8</v>
+      </c>
+      <c r="P29" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2197,23 +3010,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D86900D-2C32-5645-AB68-CC4132AD063A}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -2221,7 +3034,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2229,123 +3042,24 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F161AE9-235B-5F4F-B46B-FF7A1631F279}">
-  <sheetPr>
-    <tabColor theme="9" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="4"/>
-      <c r="B4" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="4"/>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="10"/>
-      <c r="C6" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="10"/>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="10"/>
-      <c r="C8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="10"/>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A10" s="10"/>
-    </row>
-    <row r="11" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="10"/>
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="10"/>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2356,9 +3070,108 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F161AE9-235B-5F4F-B46B-FF7A1631F279}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="C7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+    </row>
+    <row r="11" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE2BF30-140F-4537-80A7-0213412F9B4D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2378,9 +3191,9 @@
               </from>
               <to>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>107950</xdr:colOff>
+                <xdr:colOff>127000</xdr:colOff>
                 <xdr:row>6</xdr:row>
-                <xdr:rowOff>120650</xdr:rowOff>
+                <xdr:rowOff>139700</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -2399,18 +3212,18 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -2418,7 +3231,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2426,25 +3239,54 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="P15" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="P16" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="P17" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="P18" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="P19" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2453,18 +3295,18 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -2472,7 +3314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2480,18 +3322,43 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>16</v>
       </c>
@@ -2507,18 +3374,18 @@
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -2526,7 +3393,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2534,18 +3401,104 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="24" x14ac:dyDescent="0.3">
+      <c r="N10" s="19"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N15" t="s">
+        <v>78</v>
+      </c>
+      <c r="T15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+      <c r="T16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N17" t="s">
+        <v>84</v>
+      </c>
+      <c r="T17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N18" t="s">
+        <v>85</v>
+      </c>
+      <c r="T18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N19" t="s">
+        <v>86</v>
+      </c>
+      <c r="T19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N20" t="s">
+        <v>87</v>
+      </c>
+      <c r="T20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>16</v>
       </c>
@@ -2557,22 +3510,577 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5311D92A-58F7-46A0-97B3-A82EB580A854}">
+  <dimension ref="C2:Q36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" customWidth="1"/>
+    <col min="13" max="13" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="K2" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="M2" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="K3" s="21">
+        <v>1</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" s="21">
+        <v>1</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="K4" s="21">
+        <v>1</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="O4" s="21">
+        <v>1</v>
+      </c>
+      <c r="P4" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q4" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="K5" s="21">
+        <v>1</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="O5" s="21">
+        <v>1</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="K6" s="15">
+        <v>2</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="O6" s="15">
+        <v>2</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q6" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="K7" s="15">
+        <v>2</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="O7" s="15">
+        <v>2</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="K11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C13" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C14" s="21">
+        <v>1</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C15" s="21">
+        <v>1</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="21">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="C16" s="21">
+        <v>1</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="21">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="K16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C17" s="15">
+        <v>2</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="15">
+        <v>2</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="15">
+        <v>2</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C23" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="K23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C24" s="21">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" s="21">
+        <v>1</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="K24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C25" s="21">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" s="21">
+        <v>1</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C26" s="21">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="21">
+        <v>1</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="K26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="15">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="15">
+        <v>2</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10EF2490-0DE5-4282-8680-84CA7888CD45}">
+  <dimension ref="N8:R15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="8" spans="14:18" x14ac:dyDescent="0.2">
+      <c r="N8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="R8" s="20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="14:18" x14ac:dyDescent="0.2">
+      <c r="N9" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="14:18" x14ac:dyDescent="0.2">
+      <c r="N10" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="14:18" x14ac:dyDescent="0.2">
+      <c r="N11" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="14:18" x14ac:dyDescent="0.2">
+      <c r="N12" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q12" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="14:18" x14ac:dyDescent="0.2">
+      <c r="N15" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B968EA2E-41E7-8D46-8511-3A40892DDF87}">
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -2580,7 +4088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2588,54 +4096,54 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="L12" s="13" t="s">
         <v>51</v>
       </c>
       <c r="M12" s="13"/>
     </row>
-    <row r="13" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="L13" s="13" t="s">
         <v>52</v>
       </c>
       <c r="M13" s="13"/>
     </row>
-    <row r="14" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="L14" s="13" t="s">
         <v>53</v>
       </c>
       <c r="M14" s="13"/>
     </row>
-    <row r="15" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="L15" s="13" t="s">
         <v>54</v>
       </c>
       <c r="M15" s="13"/>
     </row>
-    <row r="16" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="L16" s="13" t="s">
         <v>55</v>
       </c>
       <c r="M16" s="13"/>
     </row>
-    <row r="17" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="L17" s="13" t="s">
         <v>59</v>
       </c>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>16</v>
       </c>
@@ -2644,9 +4152,14 @@
       </c>
       <c r="M18" s="13"/>
     </row>
-    <row r="19" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>135</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2655,43 +4168,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10EF2490-0DE5-4282-8680-84CA7888CD45}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59FB2D93-30E8-4ACF-9731-CE5E7474CD09}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59FB2D93-30E8-4ACF-9731-CE5E7474CD09}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA3CFC02-6145-3449-B830-66CE73569923}">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:J134"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -2699,7 +4202,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2707,24 +4210,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9"/>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>16</v>
       </c>
@@ -2732,73 +4235,19 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.2">
       <c r="J85" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B134" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D51689-B37C-0541-BD58-346F20EDF6DA}">
-  <sheetPr>
-    <tabColor theme="7" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="5"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
